--- a/Templates/BoxScores/October.xlsx
+++ b/Templates/BoxScores/October.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\Templates\BoxScores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33168671-1EB8-428D-B731-71560346C607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A107157-37F3-47BE-87C8-0B47683171A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" xr2:uid="{7901B5C0-98B5-4042-9E0B-86E022D78A84}"/>
   </bookViews>
@@ -2631,6 +2631,9 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2641,9 +2644,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2992,10 +2992,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="21"/>
       <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
@@ -3004,179 +3004,179 @@
       <c r="A2" s="7"/>
       <c r="B2" s="6"/>
       <c r="AA2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="AA3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="4"/>
       <c r="AA4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="4"/>
       <c r="AA5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="4"/>
       <c r="AA6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="4"/>
       <c r="AA7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="4"/>
       <c r="AA8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="4"/>
       <c r="AA9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="4"/>
       <c r="AA10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="4"/>
       <c r="AA11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
       <c r="AA12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="4"/>
       <c r="AA13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="4"/>
       <c r="AA14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="4"/>
       <c r="AA15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="4"/>
       <c r="AA16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="4"/>
       <c r="AA17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="4"/>
       <c r="AA18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="4"/>
       <c r="AA19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="4"/>
       <c r="AA20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="4"/>
       <c r="AA21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="4"/>
       <c r="AA22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="AA23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="AA24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="AA25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="AA26" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="AA27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="AA28" s="1" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="1:27" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3240,14 +3240,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3458,12 +3458,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="9" t="s">
         <v>46</v>
       </c>
@@ -3736,50 +3736,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="19" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="19" t="s">
+      <c r="D1" s="21"/>
+      <c r="E1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="19" t="s">
+      <c r="F1" s="21"/>
+      <c r="G1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="19" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="20"/>
-      <c r="K1" s="19" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="19" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="20"/>
-      <c r="O1" s="19" t="s">
+      <c r="N1" s="21"/>
+      <c r="O1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="19" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="20"/>
-      <c r="S1" s="19" t="s">
+      <c r="R1" s="21"/>
+      <c r="S1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="20"/>
-      <c r="U1" s="19" t="s">
+      <c r="T1" s="21"/>
+      <c r="U1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="20"/>
+      <c r="V1" s="21"/>
     </row>
     <row r="2" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
@@ -5343,50 +5343,50 @@
     </row>
     <row r="27" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="21"/>
+      <c r="C28" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="19" t="s">
+      <c r="D28" s="21"/>
+      <c r="E28" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="19" t="s">
+      <c r="F28" s="21"/>
+      <c r="G28" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="19" t="s">
+      <c r="H28" s="21"/>
+      <c r="I28" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="20"/>
-      <c r="K28" s="19" t="s">
+      <c r="J28" s="21"/>
+      <c r="K28" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="20"/>
-      <c r="M28" s="19" t="s">
+      <c r="L28" s="21"/>
+      <c r="M28" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="N28" s="20"/>
-      <c r="O28" s="19" t="s">
+      <c r="N28" s="21"/>
+      <c r="O28" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="19" t="s">
+      <c r="P28" s="21"/>
+      <c r="Q28" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R28" s="20"/>
-      <c r="S28" s="19" t="s">
+      <c r="R28" s="21"/>
+      <c r="S28" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="T28" s="20"/>
-      <c r="U28" s="19" t="s">
+      <c r="T28" s="21"/>
+      <c r="U28" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V28" s="20"/>
+      <c r="V28" s="21"/>
     </row>
     <row r="29" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
@@ -6896,46 +6896,46 @@
     </row>
     <row r="53" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="54" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="19" t="s">
+      <c r="B54" s="21"/>
+      <c r="C54" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="19" t="s">
+      <c r="D54" s="21"/>
+      <c r="E54" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="19" t="s">
+      <c r="F54" s="21"/>
+      <c r="G54" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="19" t="s">
+      <c r="H54" s="21"/>
+      <c r="I54" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="20"/>
-      <c r="K54" s="19" t="s">
+      <c r="J54" s="21"/>
+      <c r="K54" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="L54" s="20"/>
-      <c r="M54" s="19" t="s">
+      <c r="L54" s="21"/>
+      <c r="M54" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="20"/>
-      <c r="O54" s="19" t="s">
+      <c r="N54" s="21"/>
+      <c r="O54" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="19" t="s">
+      <c r="P54" s="21"/>
+      <c r="Q54" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R54" s="20"/>
-      <c r="S54" s="19" t="s">
+      <c r="R54" s="21"/>
+      <c r="S54" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="T54" s="20"/>
+      <c r="T54" s="21"/>
     </row>
     <row r="55" spans="1:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="16" t="s">
@@ -8331,29 +8331,45 @@
     </row>
     <row r="79" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="80" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
-      <c r="N80" s="23"/>
-      <c r="O80" s="23"/>
-      <c r="P80" s="23"/>
-      <c r="Q80" s="23"/>
-      <c r="R80" s="23"/>
-      <c r="S80" s="23"/>
-      <c r="T80" s="23"/>
+      <c r="A80" s="19"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="19"/>
+      <c r="M80" s="19"/>
+      <c r="N80" s="19"/>
+      <c r="O80" s="19"/>
+      <c r="P80" s="19"/>
+      <c r="Q80" s="19"/>
+      <c r="R80" s="19"/>
+      <c r="S80" s="19"/>
+      <c r="T80" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="S54:T54"/>
     <mergeCell ref="S28:T28"/>
     <mergeCell ref="U28:V28"/>
@@ -8370,22 +8386,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
